--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcEffectivenessPersonnel.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcEffectivenessPersonnel.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="按人员导出" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <t>质检员</t>
   </si>
   <si>
-    <t>质检单数量</t>
+    <t>送检数量</t>
   </si>
   <si>
     <t>完成质检</t>
@@ -583,7 +583,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
